--- a/upload/execucao2022.xlsx
+++ b/upload/execucao2022.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +537,531 @@
         <is>
           <t>Valor pago em RP</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9287853</v>
+      </c>
+      <c r="B2" t="n">
+        <v>362</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>44560</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SEAPA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO COMUNITARIA LAGOA DOS ANJICOS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>00.510.857/0001-51</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>41</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9287865</v>
+      </c>
+      <c r="B3" t="n">
+        <v>361</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>44560</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1231</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SEAPA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO DOS PEQUENOS PRODUTORES DE PORTEIRAS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25.229.337/0001-04</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9317848</v>
+      </c>
+      <c r="B4" t="n">
+        <v>953</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>44557</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CONSORCIO INTERMUNICIPAL DA BAIXA MOGIANA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>32.308.233/0001-42</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9317848</v>
+      </c>
+      <c r="B5" t="n">
+        <v>954</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>44557</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CONSORCIO INTERMUNICIPAL DA BAIXA MOGIANA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>32.308.233/0001-42</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9318235</v>
+      </c>
+      <c r="B6" t="n">
+        <v>752</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>44559</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1271</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SECULT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SETE GUARDAS DE NOSSA SENHORA DO ROSARIO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.899.142/0001-40</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>42</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>347000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9318767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>578</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>44560</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SEDESE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO DE RESGATE DA DIGNIDADE HUMANA PROVIDENCIA DIVINA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22.643.399/0001-61</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>43</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SUBVENCOES SOCIAIS</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SUBVENCOES SOCIAIS</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9318876</v>
+      </c>
+      <c r="B8" t="n">
+        <v>605</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>44560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SEDESE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO DO PEQUENO CRISTO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>42.783.621/0001-39</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>42</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>RECURSOS ORDINARIOS</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
